--- a/New_Outputs/Stats_MME_vs_ROE.xlsx
+++ b/New_Outputs/Stats_MME_vs_ROE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="76">
   <si>
     <t>scale</t>
   </si>
@@ -115,9 +115,6 @@
   </si>
   <si>
     <t>PRO-028</t>
-  </si>
-  <si>
-    <t>-Inf</t>
   </si>
   <si>
     <t>PRO-039</t>
@@ -723,37 +720,37 @@
         <v>14</v>
       </c>
       <c r="C4">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D4">
-        <v>1.315057721776518</v>
+        <v>1.279461829395317</v>
       </c>
       <c r="E4">
-        <v>-2.759314216626818</v>
+        <v>-3.427038591046125</v>
       </c>
       <c r="F4">
-        <v>0.5717527822663775</v>
+        <v>0.3879090196256496</v>
       </c>
       <c r="G4">
-        <v>0.1430740838038184</v>
+        <v>-0.0402884270209907</v>
       </c>
       <c r="H4">
-        <v>0.819792222682078</v>
+        <v>0.6957332686411623</v>
       </c>
       <c r="I4">
-        <v>0.01317420937258324</v>
+        <v>0.07444750926346595</v>
       </c>
       <c r="J4">
-        <v>0.5769085659123681</v>
+        <v>0.5181807996104849</v>
       </c>
       <c r="K4">
-        <v>0.01219078543042728</v>
+        <v>0.01349374975490988</v>
       </c>
       <c r="L4">
-        <v>1.070572013896827</v>
+        <v>1.69820284829873</v>
       </c>
       <c r="M4">
-        <v>-4.167178210219679</v>
+        <v>-5.599824314014756</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -764,37 +761,37 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D5">
-        <v>1.177832312264415</v>
+        <v>1.110932431009713</v>
       </c>
       <c r="E5">
-        <v>-4.003335533600118</v>
+        <v>-4.574738531796091</v>
       </c>
       <c r="F5">
-        <v>0.1081009429844856</v>
+        <v>0.581664058628469</v>
       </c>
       <c r="G5">
-        <v>-0.4709341535795484</v>
+        <v>0.1402215667483516</v>
       </c>
       <c r="H5">
-        <v>0.622036488582674</v>
+        <v>0.8302052111711028</v>
       </c>
       <c r="I5">
-        <v>0.7251958483871095</v>
+        <v>0.01431382904144642</v>
       </c>
       <c r="J5">
-        <v>0.08229885243868079</v>
+        <v>0.4162069525122016</v>
       </c>
       <c r="K5">
-        <v>0.7892488061161885</v>
+        <v>0.0965622393984561</v>
       </c>
       <c r="L5">
-        <v>0.1807815750742062</v>
+        <v>2.95241941879811</v>
       </c>
       <c r="M5">
-        <v>-4.216265914184573</v>
+        <v>-7.854677014081759</v>
       </c>
     </row>
   </sheetData>
@@ -863,13 +860,13 @@
         <v>21</v>
       </c>
       <c r="C4">
-        <v>1.035828902535855</v>
+        <v>0.5656563649190489</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
-        <v>0.3178272221240911</v>
+        <v>0.4570185535485144</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -880,10 +877,10 @@
         <v>22</v>
       </c>
       <c r="C5">
-        <v>1.326638808833378</v>
+        <v>-0.7257861554266368</v>
       </c>
       <c r="E5">
-        <v>0.1846281916018991</v>
+        <v>0.4679698754475058</v>
       </c>
     </row>
   </sheetData>
@@ -1012,13 +1009,13 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="s">
-        <v>33</v>
+      <c r="F6">
+        <v>-6.431798275933005</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -1038,7 +1035,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
@@ -1058,7 +1055,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -1078,7 +1075,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
@@ -1098,7 +1095,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -1118,7 +1115,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
         <v>14</v>
@@ -1138,7 +1135,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -1158,7 +1155,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
@@ -1178,7 +1175,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
@@ -1198,7 +1195,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -1212,13 +1209,13 @@
       <c r="E16">
         <v>0</v>
       </c>
-      <c r="F16" t="s">
-        <v>33</v>
+      <c r="F16">
+        <v>-6.431798275933005</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
@@ -1238,7 +1235,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
         <v>14</v>
@@ -1252,13 +1249,13 @@
       <c r="E18">
         <v>0</v>
       </c>
-      <c r="F18" t="s">
-        <v>33</v>
+      <c r="F18">
+        <v>-6.431798275933005</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
         <v>14</v>
@@ -1278,7 +1275,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
         <v>14</v>
@@ -1298,7 +1295,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
         <v>14</v>
@@ -1318,7 +1315,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
@@ -1332,13 +1329,13 @@
       <c r="E22">
         <v>0</v>
       </c>
-      <c r="F22" t="s">
-        <v>33</v>
+      <c r="F22">
+        <v>-6.431798275933005</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -1358,7 +1355,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -1372,7 +1369,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -1392,7 +1389,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1412,7 +1409,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
@@ -1432,7 +1429,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
@@ -1446,7 +1443,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
@@ -1460,7 +1457,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
@@ -1474,7 +1471,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
@@ -1494,7 +1491,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
         <v>14</v>
@@ -1514,7 +1511,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
@@ -1534,7 +1531,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
@@ -1548,7 +1545,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
         <v>14</v>
@@ -1568,7 +1565,7 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
         <v>14</v>
@@ -1582,13 +1579,13 @@
       <c r="E36">
         <v>0</v>
       </c>
-      <c r="F36" t="s">
-        <v>33</v>
+      <c r="F36">
+        <v>-6.431798275933005</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
@@ -1608,7 +1605,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B38" t="s">
         <v>14</v>
@@ -1628,7 +1625,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
@@ -1642,13 +1639,13 @@
       <c r="E39">
         <v>0</v>
       </c>
-      <c r="F39" t="s">
-        <v>33</v>
+      <c r="F39">
+        <v>-6.431798275933005</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
         <v>14</v>
@@ -1668,7 +1665,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
         <v>15</v>
@@ -1688,7 +1685,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
         <v>15</v>
@@ -1708,7 +1705,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
         <v>15</v>
@@ -1722,13 +1719,13 @@
       <c r="E43">
         <v>0</v>
       </c>
-      <c r="F43" t="s">
-        <v>33</v>
+      <c r="F43">
+        <v>-6.431798275933005</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
         <v>15</v>
@@ -1742,13 +1739,13 @@
       <c r="E44">
         <v>0</v>
       </c>
-      <c r="F44" t="s">
-        <v>33</v>
+      <c r="F44">
+        <v>-6.431798275933005</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B45" t="s">
         <v>14</v>
@@ -1768,7 +1765,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B46" t="s">
         <v>15</v>
@@ -1782,7 +1779,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
         <v>14</v>
@@ -1796,7 +1793,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B48" t="s">
         <v>15</v>
@@ -1810,7 +1807,7 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
